--- a/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Llama-3.3-70B-Instruct/metrics_default_vs_aae.xlsx
+++ b/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Llama-3.3-70B-Instruct/metrics_default_vs_aae.xlsx
@@ -426,19 +426,19 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.5704225352112676</v>
+        <v>0.5352112676056338</v>
       </c>
       <c r="D2">
-        <v>0.5596330275229358</v>
+        <v>0.6226415094339622</v>
       </c>
       <c r="E2">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="F2">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="G2">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
